--- a/attendance_filled.xlsx
+++ b/attendance_filled.xlsx
@@ -46,7 +46,7 @@
     <t>Probability and Statistics</t>
   </si>
   <si>
-    <t>SEM-1</t>
+    <t>E2-SEM-1</t>
   </si>
   <si>
     <t>CSE-E2-SEM-1-02</t>
